--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,6 +1234,801 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120401730</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102143</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>704349</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6361513</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120401720</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108811</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:87, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>704397</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6361406</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120401724</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106872</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:84, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>704343</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6361444</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120401738</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101097</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>704558</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6361540</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120401735</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102143</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>704551</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6361540</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 0,6 m hög</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120401732</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102143</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>704488</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6361510</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,6 m hög</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120401726</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102143</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:82, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>704343</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6361444</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,4 m hög</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1236,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401730</v>
+        <v>120401726</v>
       </c>
       <c r="B7" t="n">
         <v>102143</v>
@@ -1281,19 +1281,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:82, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704349</v>
+        <v>704343</v>
       </c>
       <c r="R7" t="n">
-        <v>6361513</v>
+        <v>6361444</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
+          <t>1 cm i diameter, 1,4 m hög</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401720</v>
+        <v>120401735</v>
       </c>
       <c r="B8" t="n">
-        <v>108811</v>
+        <v>102143</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,28 +1369,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1398,17 +1407,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:87, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704397</v>
+        <v>704551</v>
       </c>
       <c r="R8" t="n">
-        <v>6361406</v>
+        <v>6361540</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,6 +1447,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 0,6 m hög</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120401724</v>
+        <v>120401732</v>
       </c>
       <c r="B9" t="n">
-        <v>106872</v>
+        <v>102143</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,41 +1490,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>6037533</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:84, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>704343</v>
+        <v>704488</v>
       </c>
       <c r="R9" t="n">
-        <v>6361444</v>
+        <v>6361510</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,6 +1568,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,6 m hög</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120401738</v>
+        <v>120401720</v>
       </c>
       <c r="B10" t="n">
-        <v>101097</v>
+        <v>108811</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,41 +1611,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:87, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>704558</v>
+        <v>704397</v>
       </c>
       <c r="R10" t="n">
-        <v>6361540</v>
+        <v>6361406</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120401735</v>
+        <v>120401738</v>
       </c>
       <c r="B11" t="n">
-        <v>102143</v>
+        <v>101097</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,49 +1718,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6037533</v>
+        <v>221235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>704551</v>
+        <v>704558</v>
       </c>
       <c r="R11" t="n">
         <v>6361540</v>
@@ -1758,11 +1782,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 cm i diameter, 0,6 m hög</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120401732</v>
+        <v>120401730</v>
       </c>
       <c r="B12" t="n">
         <v>102143</v>
@@ -1834,7 +1853,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1843,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704488</v>
+        <v>704349</v>
       </c>
       <c r="R12" t="n">
-        <v>6361510</v>
+        <v>6361513</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1883,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 cm i diameter, 1,6 m hög</t>
+          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401726</v>
+        <v>120401724</v>
       </c>
       <c r="B13" t="n">
-        <v>102143</v>
+        <v>106872</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,45 +1941,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:82, Gtl</t>
+          <t>Lojsta, Bjärs 1:84, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1970,7 +1975,7 @@
         <v>6361444</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2000,11 +2005,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 cm i diameter, 1,4 m hög</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1236,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401726</v>
+        <v>120401735</v>
       </c>
       <c r="B7" t="n">
         <v>102143</v>
@@ -1286,14 +1286,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:82, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704343</v>
+        <v>704551</v>
       </c>
       <c r="R7" t="n">
-        <v>6361444</v>
+        <v>6361540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 cm i diameter, 1,4 m hög</t>
+          <t>1 cm i diameter, 0,6 m hög</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401735</v>
+        <v>120401720</v>
       </c>
       <c r="B8" t="n">
-        <v>102143</v>
+        <v>108811</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,37 +1369,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1407,17 +1398,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:87, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704551</v>
+        <v>704397</v>
       </c>
       <c r="R8" t="n">
-        <v>6361540</v>
+        <v>6361406</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,11 +1438,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 cm i diameter, 0,6 m hög</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120401732</v>
+        <v>120401724</v>
       </c>
       <c r="B9" t="n">
-        <v>102143</v>
+        <v>106872</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,55 +1476,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6037533</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:84, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>704488</v>
+        <v>704343</v>
       </c>
       <c r="R9" t="n">
-        <v>6361510</v>
+        <v>6361444</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,11 +1540,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 cm i diameter, 1,6 m hög</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120401720</v>
+        <v>120401738</v>
       </c>
       <c r="B10" t="n">
-        <v>108811</v>
+        <v>101097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,46 +1578,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:87, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>704397</v>
+        <v>704558</v>
       </c>
       <c r="R10" t="n">
-        <v>6361406</v>
+        <v>6361540</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120401738</v>
+        <v>120401732</v>
       </c>
       <c r="B11" t="n">
-        <v>101097</v>
+        <v>102143</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,38 +1680,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221235</v>
+        <v>6037533</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>704558</v>
+        <v>704488</v>
       </c>
       <c r="R11" t="n">
-        <v>6361540</v>
+        <v>6361510</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1782,6 +1758,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,6 m hög</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1789,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120401730</v>
+        <v>120401726</v>
       </c>
       <c r="B12" t="n">
         <v>102143</v>
@@ -1853,19 +1834,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:82, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704349</v>
+        <v>704343</v>
       </c>
       <c r="R12" t="n">
-        <v>6361513</v>
+        <v>6361444</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,7 +1883,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
+          <t>1 cm i diameter, 1,4 m hög</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401724</v>
+        <v>120401730</v>
       </c>
       <c r="B13" t="n">
-        <v>106872</v>
+        <v>102143</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,41 +1922,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220079</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:84, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704343</v>
+        <v>704349</v>
       </c>
       <c r="R13" t="n">
-        <v>6361444</v>
+        <v>6361513</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,6 +2000,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1236,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401735</v>
+        <v>120401730</v>
       </c>
       <c r="B7" t="n">
         <v>102143</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704551</v>
+        <v>704349</v>
       </c>
       <c r="R7" t="n">
-        <v>6361540</v>
+        <v>6361513</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 cm i diameter, 0,6 m hög</t>
+          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401720</v>
+        <v>120401724</v>
       </c>
       <c r="B8" t="n">
-        <v>108811</v>
+        <v>106872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:87, Gtl</t>
+          <t>Lojsta, Bjärs 1:84, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704397</v>
+        <v>704343</v>
       </c>
       <c r="R8" t="n">
-        <v>6361406</v>
+        <v>6361444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120401724</v>
+        <v>120401738</v>
       </c>
       <c r="B9" t="n">
-        <v>106872</v>
+        <v>101097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,41 +1471,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:84, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>704343</v>
+        <v>704558</v>
       </c>
       <c r="R9" t="n">
-        <v>6361444</v>
+        <v>6361540</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120401738</v>
+        <v>120401732</v>
       </c>
       <c r="B10" t="n">
-        <v>101097</v>
+        <v>102143</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,38 +1573,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>6037533</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>704558</v>
+        <v>704488</v>
       </c>
       <c r="R10" t="n">
-        <v>6361540</v>
+        <v>6361510</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1642,6 +1651,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,6 m hög</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120401732</v>
+        <v>120401735</v>
       </c>
       <c r="B11" t="n">
         <v>102143</v>
@@ -1722,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>704488</v>
+        <v>704551</v>
       </c>
       <c r="R11" t="n">
-        <v>6361510</v>
+        <v>6361540</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,7 +1776,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 cm i diameter, 1,6 m hög</t>
+          <t>1 cm i diameter, 0,6 m hög</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401730</v>
+        <v>120401720</v>
       </c>
       <c r="B13" t="n">
-        <v>102143</v>
+        <v>108811</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,55 +1936,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:87, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704349</v>
+        <v>704397</v>
       </c>
       <c r="R13" t="n">
-        <v>6361513</v>
+        <v>6361406</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2000,11 +2005,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401730</v>
+        <v>120401738</v>
       </c>
       <c r="B7" t="n">
-        <v>102143</v>
+        <v>101097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,52 +1248,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6037533</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704349</v>
+        <v>704558</v>
       </c>
       <c r="R7" t="n">
-        <v>6361513</v>
+        <v>6361540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,11 +1312,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401724</v>
+        <v>120401732</v>
       </c>
       <c r="B8" t="n">
-        <v>106872</v>
+        <v>102143</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,41 +1350,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>6037533</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:84, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704343</v>
+        <v>704488</v>
       </c>
       <c r="R8" t="n">
-        <v>6361444</v>
+        <v>6361510</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,6 +1428,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,6 m hög</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120401738</v>
+        <v>120401726</v>
       </c>
       <c r="B9" t="n">
-        <v>101097</v>
+        <v>102143</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,38 +1471,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>6037533</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:82, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>704558</v>
+        <v>704343</v>
       </c>
       <c r="R9" t="n">
-        <v>6361540</v>
+        <v>6361444</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,6 +1549,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,4 m hög</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120401732</v>
+        <v>120401730</v>
       </c>
       <c r="B10" t="n">
         <v>102143</v>
@@ -1606,7 +1625,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>704488</v>
+        <v>704349</v>
       </c>
       <c r="R10" t="n">
-        <v>6361510</v>
+        <v>6361513</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1655,7 +1674,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 cm i diameter, 1,6 m hög</t>
+          <t>5 cm i diameter, 4,5 m hög, flerstammig</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1803,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120401726</v>
+        <v>120401720</v>
       </c>
       <c r="B12" t="n">
-        <v>102143</v>
+        <v>108811</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,37 +1834,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1853,17 +1863,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:82, Gtl</t>
+          <t>Lojsta, Bjärs 1:87, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704343</v>
+        <v>704397</v>
       </c>
       <c r="R12" t="n">
-        <v>6361444</v>
+        <v>6361406</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,11 +1903,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 cm i diameter, 1,4 m hög</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401720</v>
+        <v>120401724</v>
       </c>
       <c r="B13" t="n">
-        <v>108811</v>
+        <v>106872</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,39 +1945,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:87, Gtl</t>
+          <t>Lojsta, Bjärs 1:84, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704397</v>
+        <v>704343</v>
       </c>
       <c r="R13" t="n">
-        <v>6361406</v>
+        <v>6361444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401738</v>
+        <v>120401720</v>
       </c>
       <c r="B7" t="n">
-        <v>101097</v>
+        <v>108811</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,41 +1248,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:87, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704558</v>
+        <v>704397</v>
       </c>
       <c r="R7" t="n">
-        <v>6361540</v>
+        <v>6361406</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401732</v>
+        <v>120401724</v>
       </c>
       <c r="B8" t="n">
-        <v>102143</v>
+        <v>106872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,55 +1355,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6037533</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:81, Gtl</t>
+          <t>Lojsta, Bjärs 1:84, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704488</v>
+        <v>704343</v>
       </c>
       <c r="R8" t="n">
-        <v>6361510</v>
+        <v>6361444</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,11 +1419,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 cm i diameter, 1,6 m hög</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1822,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120401720</v>
+        <v>120401732</v>
       </c>
       <c r="B12" t="n">
-        <v>108811</v>
+        <v>102143</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,28 +1820,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1863,17 +1858,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:87, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704397</v>
+        <v>704488</v>
       </c>
       <c r="R12" t="n">
-        <v>6361406</v>
+        <v>6361510</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,6 +1898,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 cm i diameter, 1,6 m hög</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401724</v>
+        <v>120401738</v>
       </c>
       <c r="B13" t="n">
-        <v>106872</v>
+        <v>101097</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,41 +1941,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220079</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:84, Gtl</t>
+          <t>Lojsta, Bjärs 1:81, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704343</v>
+        <v>704558</v>
       </c>
       <c r="R13" t="n">
-        <v>6361444</v>
+        <v>6361540</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>120401726</v>
       </c>
       <c r="B8" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>120401730</v>
       </c>
       <c r="B9" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>120401732</v>
       </c>
       <c r="B11" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>120401735</v>
       </c>
       <c r="B13" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>120401726</v>
       </c>
       <c r="B8" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>120401730</v>
       </c>
       <c r="B9" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>120401732</v>
       </c>
       <c r="B11" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>120401735</v>
       </c>
       <c r="B13" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>120401726</v>
       </c>
       <c r="B8" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>120401730</v>
       </c>
       <c r="B9" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>120401732</v>
       </c>
       <c r="B11" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>120401735</v>
       </c>
       <c r="B13" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>120401726</v>
       </c>
       <c r="B8" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>120401730</v>
       </c>
       <c r="B9" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>120401732</v>
       </c>
       <c r="B11" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>120401735</v>
       </c>
       <c r="B13" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>120401726</v>
       </c>
       <c r="B8" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>120401730</v>
       </c>
       <c r="B9" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>120401732</v>
       </c>
       <c r="B11" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>120401735</v>
       </c>
       <c r="B13" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>120401726</v>
       </c>
       <c r="B8" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>120401730</v>
       </c>
       <c r="B9" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>120401732</v>
       </c>
       <c r="B11" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>120401735</v>
       </c>
       <c r="B13" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2790,6 +2790,1170 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130807433</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87138</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>704322</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6361478</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130807442</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87022</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>704285</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6361518</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130807443</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90513</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>970</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bittermusseron</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leucopaxillus gentianeus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>704276</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6361505</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130807440</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87173</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>704377</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6361495</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130807432</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87046</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>704322</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6361478</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130807429</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87198</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>704326</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6361502</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130807437</v>
+      </c>
+      <c r="B27" t="n">
+        <v>87185</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>704534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6361597</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130807444</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91196</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>704536</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6361615</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130807436</v>
+      </c>
+      <c r="B29" t="n">
+        <v>87185</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>704389</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6361480</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130807439</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87173</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>704409</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6361473</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130807434</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87069</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>424</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>704395</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6361502</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130807428</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87069</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>424</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>704332</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6361483</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Dammström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Dammström, Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -2795,7 +2795,7 @@
         <v>130807433</v>
       </c>
       <c r="B21" t="n">
-        <v>87138</v>
+        <v>87139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>130807442</v>
       </c>
       <c r="B22" t="n">
-        <v>87022</v>
+        <v>87023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>130807443</v>
       </c>
       <c r="B23" t="n">
-        <v>90513</v>
+        <v>90514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>87173</v>
+        <v>87174</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>130807432</v>
       </c>
       <c r="B25" t="n">
-        <v>87046</v>
+        <v>87047</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>130807429</v>
       </c>
       <c r="B26" t="n">
-        <v>87198</v>
+        <v>87199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>130807437</v>
       </c>
       <c r="B27" t="n">
-        <v>87185</v>
+        <v>87186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>130807444</v>
       </c>
       <c r="B28" t="n">
-        <v>91196</v>
+        <v>91197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>130807436</v>
       </c>
       <c r="B29" t="n">
-        <v>87185</v>
+        <v>87186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130807439</v>
+        <v>130807434</v>
       </c>
       <c r="B30" t="n">
-        <v>87173</v>
+        <v>87070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003296</v>
+        <v>424</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>704409</v>
+        <v>704395</v>
       </c>
       <c r="R30" t="n">
-        <v>6361473</v>
+        <v>6361502</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130807434</v>
+        <v>130807439</v>
       </c>
       <c r="B31" t="n">
-        <v>87069</v>
+        <v>87174</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3773,21 +3773,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>424</v>
+        <v>6003296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>704395</v>
+        <v>704409</v>
       </c>
       <c r="R31" t="n">
-        <v>6361502</v>
+        <v>6361473</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3862,7 +3862,7 @@
         <v>130807428</v>
       </c>
       <c r="B32" t="n">
-        <v>87069</v>
+        <v>87070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3471,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130807444</v>
+        <v>130807436</v>
       </c>
       <c r="B28" t="n">
-        <v>91197</v>
+        <v>87186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704536</v>
+        <v>704389</v>
       </c>
       <c r="R28" t="n">
-        <v>6361615</v>
+        <v>6361480</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130807436</v>
+        <v>130807444</v>
       </c>
       <c r="B29" t="n">
-        <v>87186</v>
+        <v>91197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>704389</v>
+        <v>704536</v>
       </c>
       <c r="R29" t="n">
-        <v>6361480</v>
+        <v>6361615</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3471,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130807436</v>
+        <v>130807444</v>
       </c>
       <c r="B28" t="n">
-        <v>87186</v>
+        <v>91197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704389</v>
+        <v>704536</v>
       </c>
       <c r="R28" t="n">
-        <v>6361480</v>
+        <v>6361615</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130807444</v>
+        <v>130807436</v>
       </c>
       <c r="B29" t="n">
-        <v>91197</v>
+        <v>87186</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>704536</v>
+        <v>704389</v>
       </c>
       <c r="R29" t="n">
-        <v>6361615</v>
+        <v>6361480</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -2986,32 +2986,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130807443</v>
+        <v>130807440</v>
       </c>
       <c r="B23" t="n">
-        <v>90514</v>
+        <v>87174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>970</v>
+        <v>6003296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>704276</v>
+        <v>704377</v>
       </c>
       <c r="R23" t="n">
-        <v>6361505</v>
+        <v>6361495</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3083,32 +3083,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130807440</v>
+        <v>130807443</v>
       </c>
       <c r="B24" t="n">
-        <v>87174</v>
+        <v>90514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003296</v>
+        <v>970</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704377</v>
+        <v>704276</v>
       </c>
       <c r="R24" t="n">
-        <v>6361495</v>
+        <v>6361505</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -2986,32 +2986,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130807440</v>
+        <v>130807443</v>
       </c>
       <c r="B23" t="n">
-        <v>87174</v>
+        <v>90514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003296</v>
+        <v>970</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>704377</v>
+        <v>704276</v>
       </c>
       <c r="R23" t="n">
-        <v>6361495</v>
+        <v>6361505</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3083,32 +3083,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130807443</v>
+        <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>90514</v>
+        <v>87174</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>970</v>
+        <v>6003296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704276</v>
+        <v>704377</v>
       </c>
       <c r="R24" t="n">
-        <v>6361505</v>
+        <v>6361495</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130807444</v>
+        <v>130807436</v>
       </c>
       <c r="B28" t="n">
-        <v>91197</v>
+        <v>87186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704536</v>
+        <v>704389</v>
       </c>
       <c r="R28" t="n">
-        <v>6361615</v>
+        <v>6361480</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130807436</v>
+        <v>130807444</v>
       </c>
       <c r="B29" t="n">
-        <v>87186</v>
+        <v>91197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>704389</v>
+        <v>704536</v>
       </c>
       <c r="R29" t="n">
-        <v>6361480</v>
+        <v>6361615</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3086,7 +3086,7 @@
         <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>87199</v>
+        <v>87218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>130807439</v>
       </c>
       <c r="B31" t="n">
-        <v>87199</v>
+        <v>87218</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3086,7 +3086,7 @@
         <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>87218</v>
+        <v>87219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>130807439</v>
       </c>
       <c r="B31" t="n">
-        <v>87218</v>
+        <v>87219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3086,7 +3086,7 @@
         <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>87219</v>
+        <v>87222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>130807439</v>
       </c>
       <c r="B31" t="n">
-        <v>87219</v>
+        <v>87222</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3086,7 +3086,7 @@
         <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>87222</v>
+        <v>87228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>130807439</v>
       </c>
       <c r="B31" t="n">
-        <v>87222</v>
+        <v>87228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3086,7 +3086,7 @@
         <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>87228</v>
+        <v>87231</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>130807439</v>
       </c>
       <c r="B31" t="n">
-        <v>87228</v>
+        <v>87231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 445-2023 artfynd.xlsx
+++ b/artfynd/A 445-2023 artfynd.xlsx
@@ -3086,7 +3086,7 @@
         <v>130807440</v>
       </c>
       <c r="B24" t="n">
-        <v>87231</v>
+        <v>87236</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>130807439</v>
       </c>
       <c r="B31" t="n">
-        <v>87231</v>
+        <v>87236</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
